--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -698,10 +698,10 @@
     <t>closureReason</t>
   </si>
   <si>
-    <t>Organization.extension:members</t>
-  </si>
-  <si>
-    <t>members</t>
+    <t>Organization.extension:member</t>
+  </si>
+  <si>
+    <t>member</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0-ballot-2}

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1366,7 +1366,7 @@
     <t>rppsRang</t>
   </si>
   <si>
-    <t>RPPS rang (11 chiffres RPPS + 2 chiffres RANG)</t>
+    <t>RPPS rang (11 chiffres RPPS + 2 ou 3 chiffres RANG)</t>
   </si>
   <si>
     <t>Organization.identifier:rppsRang.id</t>
@@ -1384,7 +1384,7 @@
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
-    &lt;code value="INTRN"/&gt;
+    &lt;code value="RPPSRG"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4151" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4152" uniqueCount="574">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -653,14 +653,18 @@
     <t>description</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Organization.description}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Organization.description|0.1.0}
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: Additional details about the Organization that could be displayed as further information to identify the Organization beyond its name (new)</t>
+  </si>
+  <si>
+    <t>R5: `Organization.description` (new:markdown)</t>
+  </si>
+  <si>
+    <t>Element `Organization.description` has a context of Organization based on following the parent source element upwards and mapping to `Organization`.
+Element `Organization.description` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod</t>
@@ -4385,7 +4389,9 @@
       <c r="M20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -4452,7 +4458,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -4463,13 +4469,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -4491,13 +4497,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4577,13 +4583,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>78</v>
@@ -4605,16 +4611,16 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4693,13 +4699,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>78</v>
@@ -4721,16 +4727,16 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4809,13 +4815,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
@@ -4837,13 +4843,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4923,13 +4929,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>78</v>
@@ -4951,13 +4957,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5037,13 +5043,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>192</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
@@ -5065,13 +5071,13 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5151,10 +5157,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5180,16 +5186,16 @@
         <v>109</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5238,7 +5244,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5267,10 +5273,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5293,17 +5299,17 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5340,10 +5346,10 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
@@ -5352,7 +5358,7 @@
         <v>115</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5361,30 +5367,30 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5493,10 +5499,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5607,10 +5613,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5636,16 +5642,16 @@
         <v>168</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -5670,11 +5676,11 @@
         <v>78</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -5692,7 +5698,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5710,7 +5716,7 @@
         <v>191</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5721,10 +5727,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5747,19 +5753,19 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -5788,7 +5794,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5806,7 +5812,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5821,10 +5827,10 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -5835,10 +5841,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5864,16 +5870,16 @@
         <v>130</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -5886,7 +5892,7 @@
         <v>78</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>78</v>
@@ -5922,7 +5928,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5937,13 +5943,13 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5951,10 +5957,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5980,13 +5986,13 @@
         <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6000,7 +6006,7 @@
         <v>78</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>78</v>
@@ -6036,7 +6042,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6051,13 +6057,13 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -6065,10 +6071,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6091,13 +6097,13 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6148,7 +6154,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6163,13 +6169,13 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -6177,10 +6183,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6203,16 +6209,16 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6262,7 +6268,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6277,13 +6283,13 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -6291,13 +6297,13 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>78</v>
@@ -6319,17 +6325,17 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6378,7 +6384,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6387,30 +6393,30 @@
         <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6519,10 +6525,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6633,10 +6639,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6662,16 +6668,16 @@
         <v>168</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6681,7 +6687,7 @@
         <v>78</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>78</v>
@@ -6696,11 +6702,11 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>78</v>
@@ -6718,7 +6724,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6736,7 +6742,7 @@
         <v>191</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6747,10 +6753,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6773,19 +6779,19 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -6795,7 +6801,7 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>78</v>
@@ -6814,7 +6820,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>78</v>
@@ -6832,7 +6838,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6847,10 +6853,10 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6861,10 +6867,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6890,16 +6896,16 @@
         <v>130</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6909,10 +6915,10 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>78</v>
@@ -6948,7 +6954,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6963,13 +6969,13 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6977,10 +6983,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7006,13 +7012,13 @@
         <v>102</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7026,7 +7032,7 @@
         <v>78</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>78</v>
@@ -7062,7 +7068,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7077,13 +7083,13 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -7091,10 +7097,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7117,13 +7123,13 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7174,7 +7180,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7189,13 +7195,13 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -7203,10 +7209,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7229,16 +7235,16 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7288,7 +7294,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7303,13 +7309,13 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7317,13 +7323,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>78</v>
@@ -7345,17 +7351,17 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7404,7 +7410,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7413,30 +7419,30 @@
         <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7545,10 +7551,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7659,10 +7665,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7688,16 +7694,16 @@
         <v>168</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7722,11 +7728,11 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7744,7 +7750,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7762,7 +7768,7 @@
         <v>191</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7773,10 +7779,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7799,19 +7805,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7821,7 +7827,7 @@
         <v>78</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>78</v>
@@ -7840,7 +7846,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -7858,7 +7864,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7873,10 +7879,10 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7887,10 +7893,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7916,16 +7922,16 @@
         <v>130</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7935,10 +7941,10 @@
         <v>78</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>78</v>
@@ -7974,7 +7980,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7989,13 +7995,13 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8003,10 +8009,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8032,13 +8038,13 @@
         <v>102</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8052,7 +8058,7 @@
         <v>78</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>78</v>
@@ -8088,7 +8094,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8103,13 +8109,13 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -8117,10 +8123,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8143,13 +8149,13 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8200,7 +8206,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8215,13 +8221,13 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8229,10 +8235,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8255,16 +8261,16 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8314,7 +8320,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8329,13 +8335,13 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8343,13 +8349,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>78</v>
@@ -8371,17 +8377,17 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8430,7 +8436,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8439,30 +8445,30 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8571,10 +8577,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8685,10 +8691,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8714,16 +8720,16 @@
         <v>168</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8748,11 +8754,11 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8770,7 +8776,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8788,7 +8794,7 @@
         <v>191</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8799,10 +8805,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8825,19 +8831,19 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8847,7 +8853,7 @@
         <v>78</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>78</v>
@@ -8866,7 +8872,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -8884,7 +8890,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8899,10 +8905,10 @@
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -8913,10 +8919,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8942,16 +8948,16 @@
         <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8961,10 +8967,10 @@
         <v>78</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>78</v>
@@ -9000,7 +9006,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9015,13 +9021,13 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -9029,10 +9035,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9058,13 +9064,13 @@
         <v>102</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9078,7 +9084,7 @@
         <v>78</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="U61" t="s" s="2">
         <v>78</v>
@@ -9114,7 +9120,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9129,13 +9135,13 @@
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -9143,10 +9149,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9169,13 +9175,13 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9226,7 +9232,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9241,13 +9247,13 @@
         <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9255,10 +9261,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9281,16 +9287,16 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9340,7 +9346,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9355,13 +9361,13 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9369,13 +9375,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>78</v>
@@ -9397,17 +9403,17 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9456,7 +9462,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9465,30 +9471,30 @@
         <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9597,10 +9603,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9711,10 +9717,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9740,16 +9746,16 @@
         <v>168</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9774,11 +9780,11 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9796,7 +9802,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9814,7 +9820,7 @@
         <v>191</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9825,10 +9831,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9851,19 +9857,19 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9892,7 +9898,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -9910,7 +9916,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9925,10 +9931,10 @@
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -9939,10 +9945,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10051,10 +10057,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10165,10 +10171,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10194,16 +10200,16 @@
         <v>146</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10252,7 +10258,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10267,10 +10273,10 @@
         <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10281,10 +10287,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10393,10 +10399,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10507,10 +10513,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10536,16 +10542,16 @@
         <v>130</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10555,7 +10561,7 @@
         <v>78</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>78</v>
@@ -10594,7 +10600,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10609,10 +10615,10 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10623,10 +10629,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10652,13 +10658,13 @@
         <v>102</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10708,7 +10714,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10723,10 +10729,10 @@
         <v>100</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
@@ -10737,10 +10743,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10766,14 +10772,14 @@
         <v>168</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10822,7 +10828,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10837,10 +10843,10 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
@@ -10851,10 +10857,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10880,14 +10886,14 @@
         <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -10936,7 +10942,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10951,10 +10957,10 @@
         <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -10965,10 +10971,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10991,19 +10997,19 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11052,7 +11058,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11067,10 +11073,10 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
@@ -11081,10 +11087,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11110,16 +11116,16 @@
         <v>102</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11168,7 +11174,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11183,10 +11189,10 @@
         <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>78</v>
@@ -11197,10 +11203,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11226,16 +11232,16 @@
         <v>130</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -11245,10 +11251,10 @@
         <v>78</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>78</v>
@@ -11284,7 +11290,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11299,13 +11305,13 @@
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11313,10 +11319,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11342,13 +11348,13 @@
         <v>102</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11362,7 +11368,7 @@
         <v>78</v>
       </c>
       <c r="T81" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="U81" t="s" s="2">
         <v>78</v>
@@ -11398,7 +11404,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11413,13 +11419,13 @@
         <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11427,10 +11433,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11453,13 +11459,13 @@
         <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11510,7 +11516,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11525,13 +11531,13 @@
         <v>100</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11539,10 +11545,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11565,16 +11571,16 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11624,7 +11630,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11639,13 +11645,13 @@
         <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -11653,13 +11659,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>78</v>
@@ -11681,17 +11687,17 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -11740,7 +11746,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11749,30 +11755,30 @@
         <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11881,10 +11887,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11995,10 +12001,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12024,16 +12030,16 @@
         <v>168</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
@@ -12058,11 +12064,11 @@
         <v>78</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>78</v>
@@ -12080,7 +12086,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12098,7 +12104,7 @@
         <v>191</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12109,10 +12115,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12135,19 +12141,19 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -12157,7 +12163,7 @@
         <v>78</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>78</v>
@@ -12176,7 +12182,7 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>78</v>
@@ -12194,7 +12200,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12209,10 +12215,10 @@
         <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12223,10 +12229,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12252,16 +12258,16 @@
         <v>130</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -12271,10 +12277,10 @@
         <v>78</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>78</v>
@@ -12310,7 +12316,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12325,13 +12331,13 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>78</v>
@@ -12339,10 +12345,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12368,13 +12374,13 @@
         <v>102</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12388,7 +12394,7 @@
         <v>78</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>78</v>
@@ -12424,7 +12430,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12439,13 +12445,13 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>78</v>
@@ -12453,10 +12459,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12479,13 +12485,13 @@
         <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12536,7 +12542,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12551,13 +12557,13 @@
         <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -12565,10 +12571,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12591,16 +12597,16 @@
         <v>89</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12650,7 +12656,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12665,13 +12671,13 @@
         <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -12679,10 +12685,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12705,70 +12711,70 @@
         <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q93" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="R93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="P93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q93" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="R93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12783,24 +12789,24 @@
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12823,19 +12829,19 @@
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>78</v>
@@ -12864,7 +12870,7 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>78</v>
@@ -12880,7 +12886,7 @@
         <v>115</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12895,24 +12901,24 @@
         <v>100</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12938,16 +12944,16 @@
         <v>102</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -12996,7 +13002,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13005,19 +13011,19 @@
         <v>88</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13025,10 +13031,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13054,16 +13060,16 @@
         <v>102</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
@@ -13112,7 +13118,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13130,7 +13136,7 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13141,10 +13147,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13167,19 +13173,19 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -13228,7 +13234,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13237,19 +13243,19 @@
         <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>78</v>
@@ -13257,10 +13263,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13283,19 +13289,19 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
@@ -13344,7 +13350,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13353,19 +13359,19 @@
         <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
@@ -13373,10 +13379,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13399,17 +13405,17 @@
         <v>89</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13458,7 +13464,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13473,10 +13479,10 @@
         <v>100</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>106</v>
@@ -13487,10 +13493,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13599,10 +13605,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13713,10 +13719,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13742,13 +13748,13 @@
         <v>102</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13798,7 +13804,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13807,7 +13813,7 @@
         <v>88</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>100</v>
@@ -13827,10 +13833,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13856,13 +13862,13 @@
         <v>130</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13892,7 +13898,7 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>78</v>
@@ -13910,7 +13916,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -13939,10 +13945,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13965,16 +13971,16 @@
         <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14024,7 +14030,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14042,7 +14048,7 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14053,10 +14059,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14082,13 +14088,13 @@
         <v>102</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14138,7 +14144,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14167,10 +14173,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14193,19 +14199,19 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
@@ -14254,7 +14260,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14272,7 +14278,7 @@
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14283,10 +14289,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14395,10 +14401,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14509,14 +14515,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -14538,16 +14544,16 @@
         <v>109</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -14596,7 +14602,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14625,10 +14631,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14651,17 +14657,17 @@
         <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -14689,10 +14695,10 @@
         <v>150</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>78</v>
@@ -14710,7 +14716,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -14728,7 +14734,7 @@
         <v>78</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -14739,10 +14745,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14765,17 +14771,17 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -14824,7 +14830,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -14839,10 +14845,10 @@
         <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -14853,10 +14859,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14879,17 +14885,17 @@
         <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>78</v>
@@ -14938,7 +14944,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -14953,10 +14959,10 @@
         <v>100</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -14967,10 +14973,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14993,17 +14999,17 @@
         <v>78</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15052,7 +15058,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15067,10 +15073,10 @@
         <v>100</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -15081,10 +15087,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15107,17 +15113,17 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15166,7 +15172,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}name-or-identifier:identifier or name SHALL be present {identifier.exists() or name.exists()}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -773,7 +773,7 @@
 </t>
   </si>
   <si>
-    <t>Identifies this organization  across multiple systems</t>
+    <t>Organization business identifier</t>
   </si>
   <si>
     <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
@@ -1442,7 +1442,7 @@
     <t>Organization.type</t>
   </si>
   <si>
-    <t>Kind of organization</t>
+    <t>Organization type</t>
   </si>
   <si>
     <t>The kind(s) of organization that this is.</t>
@@ -1515,7 +1515,7 @@
 </t>
   </si>
   <si>
-    <t>A contact detail for the organization</t>
+    <t>Organization telecom</t>
   </si>
   <si>
     <t>A contact detail for the organization.</t>
@@ -1587,7 +1587,7 @@
 </t>
   </si>
   <si>
-    <t>The organization of which this organization forms a part</t>
+    <t>The organization of which this organization is part of: e.g. an ERN</t>
   </si>
   <si>
     <t>The organization of which this organization forms a part.</t>
@@ -1686,7 +1686,7 @@
 </t>
   </si>
   <si>
-    <t>Contact for the organization for a certain purpose</t>
+    <t>Organization contact infos</t>
   </si>
   <si>
     <t>Contact for the organization for a certain purpose.</t>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>88</v>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-etablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
